--- a/data/trans_bre/P2C_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,26</t>
+          <t>-2,95; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 17,23</t>
+          <t>4,86; 18,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 15,63</t>
+          <t>2,38; 15,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 8,05</t>
+          <t>-2,65; 8,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 44,01</t>
+          <t>-13,73; 42,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 54,14</t>
+          <t>12,46; 59,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,65; 81,55</t>
+          <t>9,68; 74,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 197,97</t>
+          <t>-36,18; 208,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 27,38</t>
+          <t>16,2; 26,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,69; 32,46</t>
+          <t>21,75; 33,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 25,38</t>
+          <t>14,35; 25,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 12,55</t>
+          <t>-1,6; 12,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,15; 102,79</t>
+          <t>49,61; 100,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,85; 90,26</t>
+          <t>51,22; 90,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,08; 72,73</t>
+          <t>34,88; 73,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 134,71</t>
+          <t>-8,5; 124,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,41</t>
+          <t>-2,15; 9,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 12,0</t>
+          <t>2,63; 11,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,85</t>
+          <t>5,01; 15,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 6,28</t>
+          <t>-4,84; 6,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 18,06</t>
+          <t>-3,6; 17,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 16,8</t>
+          <t>3,49; 16,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 29,99</t>
+          <t>8,38; 29,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 34,37</t>
+          <t>-21,75; 34,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,75; -1,62</t>
+          <t>-12,89; -1,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -2,0</t>
+          <t>-13,77; -1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 5,25</t>
+          <t>-5,41; 5,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 10,97</t>
+          <t>-1,29; 10,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,08; -4,67</t>
+          <t>-36,05; -4,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,54; -3,6</t>
+          <t>-24,85; -3,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 18,62</t>
+          <t>-16,03; 17,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 250,7</t>
+          <t>-8,69; 219,65</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,46</t>
+          <t>1,76; 11,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 3,02</t>
+          <t>-9,24; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 6,05</t>
+          <t>-2,93; 6,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 4,45</t>
+          <t>-1,12; 4,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,97; 144,09</t>
+          <t>11,77; 123,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 12,86</t>
+          <t>-31,06; 15,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 58,57</t>
+          <t>-19,08; 59,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 64,41</t>
+          <t>-12,12; 65,26</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 12,1</t>
+          <t>1,66; 12,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 9,23</t>
+          <t>-4,17; 9,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 11,01</t>
+          <t>0,25; 11,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 66,94</t>
+          <t>1,85; 64,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,06; 152,07</t>
+          <t>9,49; 150,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 46,4</t>
+          <t>-14,9; 52,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 123,56</t>
+          <t>0,74; 128,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,88; 1162,11</t>
+          <t>20,59; 994,22</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 7,63</t>
+          <t>-6,57; 7,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 18,99</t>
+          <t>1,42; 18,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 17,31</t>
+          <t>2,3; 17,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 15,14</t>
+          <t>5,19; 15,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 42,28</t>
+          <t>-25,92; 43,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 61,11</t>
+          <t>3,17; 57,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 74,98</t>
+          <t>7,27; 73,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,06; 81,94</t>
+          <t>20,95; 82,67</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,64</t>
+          <t>3,11; 7,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,63</t>
+          <t>4,44; 9,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,87</t>
+          <t>5,2; 9,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,97; 24,36</t>
+          <t>4,08; 24,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,14</t>
+          <t>10,26; 27,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 22,37</t>
+          <t>9,73; 21,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,69; 33,01</t>
+          <t>15,81; 32,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,74; 208,36</t>
+          <t>31,86; 234,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 7,07</t>
+          <t>-2,99; 7,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 18,18</t>
+          <t>4,62; 17,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 15,13</t>
+          <t>3,14; 14,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 8,38</t>
+          <t>-2,98; 8,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 42,67</t>
+          <t>-13,65; 44,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 59,32</t>
+          <t>12,18; 56,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 74,46</t>
+          <t>12,12; 72,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 208,07</t>
+          <t>-34,0; 165,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,38</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 26,96</t>
+          <t>16,27; 26,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,75; 33,17</t>
+          <t>21,23; 31,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 25,66</t>
+          <t>14,65; 25,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 12,23</t>
+          <t>2,44; 12,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,61; 100,12</t>
+          <t>50,74; 98,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,22; 90,18</t>
+          <t>50,03; 89,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,88; 73,78</t>
+          <t>35,47; 74,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 124,36</t>
+          <t>12,61; 122,89</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 9,04</t>
+          <t>-1,42; 9,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,78</t>
+          <t>2,98; 11,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 15,6</t>
+          <t>4,75; 14,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,34</t>
+          <t>-1,45; 8,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 17,09</t>
+          <t>-2,36; 18,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 16,38</t>
+          <t>4,04; 16,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 29,55</t>
+          <t>8,39; 28,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 34,97</t>
+          <t>-6,28; 44,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -1,51</t>
+          <t>-12,81; -0,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,77; -1,57</t>
+          <t>-13,82; -1,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 5,14</t>
+          <t>-4,88; 5,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 10,69</t>
+          <t>-3,03; 3,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,05; -4,66</t>
+          <t>-35,99; -3,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -3,12</t>
+          <t>-24,75; -3,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 17,92</t>
+          <t>-14,38; 19,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 219,65</t>
+          <t>-18,03; 29,64</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,76</t>
+          <t>1,3; 11,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 3,32</t>
+          <t>-8,71; 3,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,17</t>
+          <t>-3,29; 6,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,65</t>
+          <t>-0,62; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 123,57</t>
+          <t>7,96; 127,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 15,05</t>
+          <t>-29,09; 13,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 59,14</t>
+          <t>-22,3; 60,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 65,26</t>
+          <t>-6,23; 77,09</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>386,13%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 12,04</t>
+          <t>1,74; 12,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 9,82</t>
+          <t>-4,67; 9,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 11,01</t>
+          <t>0,45; 10,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 64,51</t>
+          <t>0,21; 6,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,49; 150,28</t>
+          <t>11,12; 153,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 52,54</t>
+          <t>-17,29; 45,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 128,16</t>
+          <t>1,35; 112,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,59; 994,22</t>
+          <t>0,19; 94,99</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>10,68</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 7,64</t>
+          <t>-7,25; 7,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 18,24</t>
+          <t>1,58; 18,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 17,44</t>
+          <t>1,82; 17,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,19</t>
+          <t>5,33; 15,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 43,91</t>
+          <t>-27,47; 39,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 57,61</t>
+          <t>3,51; 59,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 73,99</t>
+          <t>5,1; 74,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,95; 82,67</t>
+          <t>21,96; 86,32</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,68</t>
+          <t>3,04; 7,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 9,13</t>
+          <t>4,29; 9,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,97</t>
+          <t>5,07; 9,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,31</t>
+          <t>2,87; 6,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,26; 27,4</t>
+          <t>10,01; 28,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,73; 21,1</t>
+          <t>9,28; 20,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,81; 32,61</t>
+          <t>15,87; 31,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,86; 234,0</t>
+          <t>19,5; 49,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
